--- a/docs/Kエナジー_DD/Kエナジー_DD状況_リスク一覧.xlsx
+++ b/docs/Kエナジー_DD/Kエナジー_DD状況_リスク一覧.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="リスク一覧" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="根拠" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DD進捗（案件リスト転記）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変電所状況" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DD進捗（案件リスト転記）" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +34,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
     </font>
   </fonts>
   <fills count="6">
@@ -49,7 +54,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -59,7 +64,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -104,6 +109,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -499,7 +519,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>凡例：緑=低／黄=中／赤=高。数値の根拠は「根拠」シート。ハザード・区域は国交省 不動産情報ライブラリ、道路は国土地理院 道路中心線、変電所は社内変電所DBによる自動判定。</t>
+          <t>凡例：緑=低／黄=中／赤=高。根拠は「根拠」シート、変電所の数字は「変電所状況」シート。</t>
         </is>
       </c>
     </row>
@@ -572,89 +592,89 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>猪苗代</t>
+          <t>北茨城</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>福島県耶麻郡猪苗代町大字磐根字大谷地4100-29</t>
+          <t>茨城県北茨城市磯原町木皿字下ノ平703</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>東北</t>
+          <t>東京</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>①座標と地番（磐根4100-29）の照合 ②町の垂直積雪量を確認 ③県道から約740mの進入ルートを現地で確認</t>
+          <t>①座標と地番（木皿703）の照合 ②県立自然公園の区域図確認 ③約1.2kmの狭い道を通る輸送ルートを現地踏査 ④接続検討の前に空容量を確認（近隣は空容量0）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>北茨城</t>
+          <t>伊豆の国</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>茨城県北茨城市磯原町木皿字下ノ平703</t>
+          <t>静岡県伊豆の国市浮橋字土澤1600-107</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>東京</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -666,102 +686,102 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>①座標と地番（木皿703）の照合 ②県立自然公園の区域図確認 ③約1.2kmの狭い道を通る輸送ルートを現地踏査 ④接続検討の前に空容量を確認（近隣は空容量0）</t>
+          <t>①伊豆の国市へ開発許可の事前相談（市街化調整区域） ②田方154kVに余裕がないため接続可否を電力会社へ事前相談 ③丘の上の造成計画（切土・盛土量）を概算</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>伊豆の国</t>
+          <t>猪苗代</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>静岡県伊豆の国市浮橋字土澤1600-107</t>
+          <t>福島県耶麻郡猪苗代町大字磐根字大谷地4100-29</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>中部</t>
+          <t>東北</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>①伊豆の国市へ開発許可の事前相談（市街化調整区域） ②丘の上の造成計画（切土・盛土量）を概算 ③田方変電所への接続可否を確認</t>
+          <t>①座標と地番（磐根4100-29）の照合 ②町の垂直積雪量を確認 ③県道から約740mの進入ルートを現地で確認</t>
         </is>
       </c>
     </row>
@@ -784,7 +804,7 @@
           <t>東北</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -799,34 +819,34 @@
           <t>低</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>①県道から約760mの進入ルート確認 ②造成計画の概算 ③東山変電所で接続検討を申込</t>
+          <t>①東山変電所の上位系（水沢275kV）の増強リスクを電力会社へ事前相談 ②県道から約760mの進入ルート確認 ③造成計画の概算</t>
         </is>
       </c>
     </row>
@@ -849,12 +869,12 @@
           <t>東北</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -864,7 +884,7 @@
           <t>低</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -874,12 +894,12 @@
           <t>低</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -914,7 +934,7 @@
           <t>東北</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -929,19 +949,19 @@
           <t>低</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -956,7 +976,7 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>①幅3m未満の進入路の拡幅要否を確認 ②接続先（中村／駒ヶ嶺）の比較</t>
+          <t>①接続先の比較（中村66kVは空容量3MW、駒ヶ嶺154kVは新駒線増強待ち） ②幅3m未満の進入路の拡幅要否を確認</t>
         </is>
       </c>
     </row>
@@ -979,7 +999,7 @@
           <t>九州</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -994,19 +1014,19 @@
           <t>低</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1126,7 +1146,7 @@
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>最寄 更科変電所(66kV) 2.0km・スコアC・N-1電制不可・出力制御あり</t>
+          <t>最寄の更科(66kV・2.0km)は空容量わずか2MW。空容量14MWの滝沢(66kV)は8.6km、会津(154kV・N-1可)は10.8km。東北は上位系の空容量データなし</t>
         </is>
       </c>
       <c r="H2" s="10" t="inlineStr">
@@ -1171,7 +1191,7 @@
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>近隣の木皿・手綱・磯原変電所(66kV)はいずれも空容量0（除外ランク）</t>
+          <t>周辺の66kV変電所4か所（木皿・手綱・磯原・五浦）はすべて上位系考慮の空容量0。常磐(275kV・12km)も潮流が運用容量を超過</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
@@ -1216,7 +1236,7 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>田方変電所(154kV) 4.6km・N-1電制可。近くの韮山・長岡は空容量0</t>
+          <t>田方(154kV・4.6km)は潮流が運用容量と同じ486MWで余裕なし。周辺の66kV（韮山・長岡・網代）は上位系考慮の空容量0</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
@@ -1261,7 +1281,7 @@
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>東山変電所(66kV) 1.9km・スコアB</t>
+          <t>東山(66kV・1.9km)は空容量10MW・スコアB。ただし上位の水沢(275kV)は潮流が運用容量を超過し、近隣の奥州市の実績で上位系増強（負担金50〜81億円）が出ている</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
@@ -1306,7 +1326,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>千厩変電所(66kV) 3.8km・スコアC</t>
+          <t>千厩(66kV・3.8km)は空容量5MW・スコアC。藤沢(66kV・空容量9MW)は8.4km。上位系の混雑は東山案件と同じ系統の可能性あり</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -1351,7 +1371,7 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>中村変電所(66kV) 4.6km・スコアC。駒ヶ嶺(154kV・N-1可)は10km</t>
+          <t>中村(66kV・4.6km)は空容量3MW。駒ヶ嶺(154kV・10km)は潮流が運用容量の約1.8倍で、実績でも154kV新駒線の増強待ち（17か月）</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
@@ -1396,7 +1416,7 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>加治木変電所(66kV) 4.9km・空容量 約7MW・スコアB</t>
+          <t>加治木(66kV・4.9km)は空容量9MW（上位系考慮7MW）・出力制御なし・スコアB。特高の規模によっては7MWが上限になる</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -1421,66 +1441,2383 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:P44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>地点</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>系統判定</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>変電所</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>距離(km)</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>最高電圧(kV)</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>運用容量(MW)</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>予想潮流(MW)</t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
+          <t>混雑度</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t>空容量(MW)</t>
+        </is>
+      </c>
+      <c r="K1" s="11" t="inlineStr">
+        <is>
+          <t>上位系考慮 空容量(MW)</t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t>N-1電制</t>
+        </is>
+      </c>
+      <c r="M1" s="11" t="inlineStr">
+        <is>
+          <t>出力制御</t>
+        </is>
+      </c>
+      <c r="N1" s="11" t="inlineStr">
+        <is>
+          <t>スコア/ランク</t>
+        </is>
+      </c>
+      <c r="O1" s="11" t="inlineStr">
+        <is>
+          <t>座標の出所</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>近くの接続検討実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="n">
+        <v>1745</v>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>猪苗代</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>更科変電所</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G2" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="J2" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" s="12" t="n"/>
+      <c r="L2" s="12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N2" s="12" t="inlineStr">
+        <is>
+          <t>33/C</t>
+        </is>
+      </c>
+      <c r="O2" s="12" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致)</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="n">
+        <v>1745</v>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>猪苗代</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr"/>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>猪苗代変電所</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" s="12" t="n"/>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>46/B</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致)</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="n">
+        <v>1745</v>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>猪苗代</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr"/>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>滝沢変電所</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K4" s="12" t="n"/>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>46/B</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致)</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="n">
+        <v>1745</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>猪苗代</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr"/>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>会津変電所</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>154</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>203</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>-95</v>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>23/データ無</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="n">
+        <v>1745</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>猪苗代</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>若松変電所</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>154</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>228</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>-52</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="n"/>
+      <c r="N6" s="12" t="inlineStr"/>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="n"/>
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>最寄の更科(66kV・2.0km)は空容量わずか2MW。空容量14MWの滝沢(66kV)は8.6km、会津(154kV・N-1可)は10.8km。東北は上位系の空容量データなし</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="12" t="n"/>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="12" t="n"/>
+      <c r="N7" s="12" t="n"/>
+      <c r="O7" s="12" t="n"/>
+      <c r="P7" s="10" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="n">
+        <v>1746</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>北茨城</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>木皿変電所</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>不可 #3</t>
+        </is>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N8" s="12" t="inlineStr">
+        <is>
+          <t>4/除外</t>
+        </is>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>1746</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>北茨城</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr"/>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>手綱変電所</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>-47</v>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>不可 #3</t>
+        </is>
+      </c>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N9" s="12" t="inlineStr">
+        <is>
+          <t>4/除外</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="n">
+        <v>1746</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>北茨城</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr"/>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>磯原変電所</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>不可 #3</t>
+        </is>
+      </c>
+      <c r="M10" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N10" s="12" t="inlineStr">
+        <is>
+          <t>4/除外</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>1746</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>北茨城</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr"/>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>五浦変電所</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>-38</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>不可 #3</t>
+        </is>
+      </c>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <t>4/除外</t>
+        </is>
+      </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="n">
+        <v>1746</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>北茨城</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr"/>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>常磐変電所</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>275</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>600</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>-683</v>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>114%</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="M12" s="12" t="n"/>
+      <c r="N12" s="12" t="inlineStr"/>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>1746</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>北茨城</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr"/>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>いわき変電所</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>275</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>669</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>-296</v>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="M13" s="12" t="n"/>
+      <c r="N13" s="12" t="inlineStr"/>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>周辺の66kV変電所4か所（木皿・手綱・磯原・五浦）はすべて上位系考慮の空容量0。常磐(275kV・12km)も潮流が運用容量を超過</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="12" t="n"/>
+      <c r="N14" s="12" t="n"/>
+      <c r="O14" s="12" t="n"/>
+      <c r="P14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n">
+        <v>1747</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>伊豆の国</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>田方変電所</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>154</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>486</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>-486</v>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N15" s="12" t="inlineStr">
+        <is>
+          <t>14/データ無</t>
+        </is>
+      </c>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n">
+        <v>1747</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>伊豆の国</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr"/>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>韮山変電所</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>不可 #3</t>
+        </is>
+      </c>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N16" s="12" t="inlineStr">
+        <is>
+          <t>19/除外</t>
+        </is>
+      </c>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測(名称一致)</t>
+        </is>
+      </c>
+      <c r="P16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>1747</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>伊豆の国</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr"/>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>長岡変電所</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>不可 #3</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N17" s="12" t="inlineStr">
+        <is>
+          <t>8/除外</t>
+        </is>
+      </c>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致)</t>
+        </is>
+      </c>
+      <c r="P17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="n">
+        <v>1747</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>伊豆の国</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr"/>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>網代変電所</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>不可 #3</t>
+        </is>
+      </c>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N18" s="12" t="inlineStr">
+        <is>
+          <t>8/除外</t>
+        </is>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致)</t>
+        </is>
+      </c>
+      <c r="P18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n">
+        <v>1747</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>伊豆の国</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr"/>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>駿東変電所</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>154</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>582</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="12" t="inlineStr"/>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="n"/>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>田方(154kV・4.6km)は潮流が運用容量と同じ486MWで余裕なし。周辺の66kV（韮山・長岡・網代）は上位系考慮の空容量0</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="12" t="n"/>
+      <c r="N20" s="12" t="n"/>
+      <c r="O20" s="12" t="n"/>
+      <c r="P20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>1748</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>一関・東山</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>東山変電所</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N21" s="12" t="inlineStr">
+        <is>
+          <t>36/B</t>
+        </is>
+      </c>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P21" s="10" t="inlineStr">
+        <is>
+          <t>前沢変電所(14.6km) 【保留】/049_奥州市前沢字狐石484-1（岩手県）_高圧蓄電所：80.80億円(税込)・入金後6ヶ月
+伊手変電所(18.3km) 【保留】/065_奥州市江刺藤里字外ノ沢539（岩手県）_高圧蓄電所：49.90億円(税込)・入金後36ヶ月</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>1748</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>一関・東山</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr"/>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>水沢変電所</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>275</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>342</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>-499</v>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>146%</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="M22" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N22" s="12" t="inlineStr">
+        <is>
+          <t>14/データ無</t>
+        </is>
+      </c>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>1748</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>一関・東山</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr"/>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>千厩変電所</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="M23" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N23" s="12" t="inlineStr">
+        <is>
+          <t>23/C</t>
+        </is>
+      </c>
+      <c r="O23" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>1748</v>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>一関・東山</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr"/>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>平泉変電所</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="M24" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N24" s="12" t="inlineStr">
+        <is>
+          <t>47/B</t>
+        </is>
+      </c>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="n">
+        <v>1748</v>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>一関・東山</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr"/>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>一関変電所</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>154</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>228</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>-204</v>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="M25" s="12" t="n"/>
+      <c r="N25" s="12" t="inlineStr"/>
+      <c r="O25" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="n"/>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>東山(66kV・1.9km)は空容量10MW・スコアB。ただし上位の水沢(275kV)は潮流が運用容量を超過し、近隣の奥州市の実績で上位系増強（負担金50〜81億円）が出ている</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+      <c r="N26" s="12" t="n"/>
+      <c r="O26" s="12" t="n"/>
+      <c r="P26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="n">
+        <v>1749</v>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>一関・千厩</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>千厩変電所</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="M27" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="inlineStr">
+        <is>
+          <t>23/C</t>
+        </is>
+      </c>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="n">
+        <v>1749</v>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>一関・千厩</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr"/>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>藤沢変電所</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="M28" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N28" s="12" t="inlineStr">
+        <is>
+          <t>41/B</t>
+        </is>
+      </c>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="n">
+        <v>1749</v>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>一関・千厩</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr"/>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>東山変電所</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N29" s="12" t="inlineStr">
+        <is>
+          <t>36/B</t>
+        </is>
+      </c>
+      <c r="O29" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="n">
+        <v>1749</v>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>一関・千厩</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr"/>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>気仙沼変電所</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>154</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>114</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>-46</v>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="M30" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N30" s="12" t="inlineStr">
+        <is>
+          <t>23/データ無</t>
+        </is>
+      </c>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="n">
+        <v>1749</v>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>一関・千厩</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr"/>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>水沢変電所</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>275</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>342</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>-499</v>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>146%</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="M31" s="12" t="n"/>
+      <c r="N31" s="12" t="inlineStr"/>
+      <c r="O31" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="n"/>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>千厩(66kV・3.8km)は空容量5MW・スコアC。藤沢(66kV・空容量9MW)は8.4km。上位系の混雑は東山案件と同じ系統の可能性あり</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="12" t="n"/>
+      <c r="P32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="n">
+        <v>1750</v>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>相馬</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>中村変電所</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="M33" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N33" s="12" t="inlineStr">
+        <is>
+          <t>19/C</t>
+        </is>
+      </c>
+      <c r="O33" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P33" s="10" t="inlineStr">
+        <is>
+          <t>駒ヶ嶺変電所(10.1km) 新地町駒ケ嶺字桜下51-1（福島県）_高圧蓄電所：3,210万円(税込)・入金後17ヶ月</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="n">
+        <v>1750</v>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>相馬</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr"/>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>駒ヶ嶺変電所</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>154</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>114</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>-204</v>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>179%</t>
+        </is>
+      </c>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="12" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="M34" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N34" s="12" t="inlineStr">
+        <is>
+          <t>14/データ無</t>
+        </is>
+      </c>
+      <c r="O34" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="n">
+        <v>1750</v>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>相馬</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr"/>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>鹿島変電所</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="M35" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N35" s="12" t="inlineStr">
+        <is>
+          <t>23/C</t>
+        </is>
+      </c>
+      <c r="O35" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P35" s="10" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="n">
+        <v>1750</v>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>相馬</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr"/>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>新地変電所</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>342</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>-418</v>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>122%</t>
+        </is>
+      </c>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="M36" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N36" s="12" t="inlineStr">
+        <is>
+          <t>19/データ無</t>
+        </is>
+      </c>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致)</t>
+        </is>
+      </c>
+      <c r="P36" s="10" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="n"/>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>中村(66kV・4.6km)は空容量3MW。駒ヶ嶺(154kV・10km)は潮流が運用容量の約1.8倍で、実績でも154kV新駒線の増強待ち（17か月）</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="12" t="n"/>
+      <c r="M37" s="12" t="n"/>
+      <c r="N37" s="12" t="n"/>
+      <c r="O37" s="12" t="n"/>
+      <c r="P37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="n">
+        <v>1751</v>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>姶良</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>加治木変電所</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="H38" s="12" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L38" s="12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="M38" s="12" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="N38" s="12" t="inlineStr">
+        <is>
+          <t>42/B</t>
+        </is>
+      </c>
+      <c r="O38" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="n">
+        <v>1751</v>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>姶良</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr"/>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>帖佐変電所</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>-54</v>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="M39" s="12" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="N39" s="12" t="inlineStr">
+        <is>
+          <t>10/除外</t>
+        </is>
+      </c>
+      <c r="O39" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P39" s="10" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="n">
+        <v>1751</v>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>姶良</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr"/>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>隼人変電所</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="J40" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="M40" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N40" s="12" t="inlineStr">
+        <is>
+          <t>19/除外</t>
+        </is>
+      </c>
+      <c r="O40" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測(名称一致)</t>
+        </is>
+      </c>
+      <c r="P40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="n">
+        <v>1751</v>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>姶良</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr"/>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>国分変電所</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>-70</v>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="M41" s="12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="N41" s="12" t="inlineStr">
+        <is>
+          <t>15/除外</t>
+        </is>
+      </c>
+      <c r="O41" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測(名称一致)</t>
+        </is>
+      </c>
+      <c r="P41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="n">
+        <v>1751</v>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>姶良</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr"/>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>霧島変電所</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>508</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>-697</v>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>137%</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="12" t="n"/>
+      <c r="L42" s="12" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="M42" s="12" t="n"/>
+      <c r="N42" s="12" t="inlineStr"/>
+      <c r="O42" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P42" s="10" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="n">
+        <v>1751</v>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>姶良</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr"/>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>鹿児島変電所</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>296</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>-222</v>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="J43" s="12" t="n"/>
+      <c r="K43" s="12" t="n"/>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="M43" s="12" t="n"/>
+      <c r="N43" s="12" t="inlineStr"/>
+      <c r="O43" s="12" t="inlineStr">
+        <is>
+          <t>OSM実測</t>
+        </is>
+      </c>
+      <c r="P43" s="10" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="n"/>
+      <c r="B44" s="12" t="n"/>
+      <c r="C44" s="12" t="n"/>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>加治木(66kV・4.9km)は空容量9MW（上位系考慮7MW）・出力制御なし・スコアB。特高の規模によっては7MWが上限になる</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="12" t="n"/>
+      <c r="G44" s="12" t="n"/>
+      <c r="H44" s="12" t="n"/>
+      <c r="I44" s="12" t="n"/>
+      <c r="J44" s="12" t="n"/>
+      <c r="K44" s="12" t="n"/>
+      <c r="L44" s="12" t="n"/>
+      <c r="M44" s="12" t="n"/>
+      <c r="N44" s="12" t="n"/>
+      <c r="O44" s="12" t="n"/>
+      <c r="P44" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>地点</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>起票日</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>DDステータス</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>輸送確認</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>輸送判定</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>輸送メモ</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>接続検討</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>地権者交渉</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>土地種別</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>緯度</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>経度</t>
         </is>

--- a/docs/Kエナジー_DD/Kエナジー_DD状況_リスク一覧.xlsx
+++ b/docs/Kエナジー_DD/Kエナジー_DD状況_リスク一覧.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="リスク一覧" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="根拠" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変電所状況" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DD進捗（案件リスト転記）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特高優先順位" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="リスク一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="根拠" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変電所状況" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DD進捗（案件リスト転記）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -80,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -126,6 +127,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -491,6 +501,494 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>特高としての優先順位（KE特高系統用蓄電池リスト 2026-09-29 の地積・地目＋送電線距離を加味）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>順位</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>地点</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>地目</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>地積(㎡)</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>最寄り送電線(kV)</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>送電線まで(m)</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>総合リスク</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>ひとこと</t>
+        </is>
+      </c>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>良い点</t>
+        </is>
+      </c>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>懸念</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>1749</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>一関・千厩</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>原野</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>31759</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>154</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>154kVの送電線まで約14m。土地3.2haの原野で、道路も良い</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>・154kV送電線（2回線）が敷地のすぐ横（約14m）
+・3.2haの原野。山林ではないので林地開発の負担が小さい見込み
+・幅5.5m以上の道路まで約40mで、7件中いちばん運びやすい</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>・上位の一関(154kV)は混雑度89%、水沢(275kV)は超過。近くの奥州市では上位系増強の回答が出ている
+・土砂警戒区域まで約200m、盛土造成地まで約100m</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>1745</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>猪苗代</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>山林</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>4926</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>154</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>154kVの送電線まで約26m。平坦で、上位の会津変電所にも余裕あり</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>・154kV送電線（2回線）まで約26m
+・上位の会津(154kV)は混雑度47%で、7件中いちばん余裕がある
+・高低差10mで平坦。ハザード・法規制も問題なし</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>・土地が0.49haと狭く、規模は小さめになる
+・多雪地域
+・座標の位置（更科）と地番（磐根）が合っていない→送電線との距離も座標が前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>1748</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>一関・東山</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>山林</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>20480</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>154</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>154kVの送電線まで約10m（3回線）。千厩と同じ上位系の混雑が課題</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>・154kV送電線まで約10m
+・2.0haあり中規模が可能</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>・上位系の混雑は千厩と同じ（一関・水沢）
+・山林2.0haで、1haを超えるため林地開発許可が必要になる可能性が高い
+・幅5.5m以上の道路まで約760m</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>相馬</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>山林</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>269499</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>土地は27haと広いが、近くの送電線は66kVで、上位の駒ヶ嶺は増強待ち</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>・66kV送電線まで約12m
+・27haと広く、敷地の取り方に自由度がある</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>・66kVなので受け入れられる規模に限りがある。中村(66kV)は空容量3MW
+・駒ヶ嶺(154kV)は混雑度179%で、154kV新駒線の増強待ち（実績17か月）
+・山林27ha→林地開発許可が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>1747</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>伊豆の国</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>原野</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>27058</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>66kVの送電線が敷地上空（約2m）を通るが、市街化調整区域で系統にも余裕がない</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>・66kV送電線が敷地の真上（約2m）
+・2.7haの原野</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>・市街化調整区域で開発許可が必要になり得る
+・周辺の66kVは空容量0、田方(154kV)は混雑度100%
+・丘の上で高低差46m</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>見送り候補</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>1751</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>姶良</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>山林</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>545133</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>4383</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>近くに送電線がない（KE表記も「鉄塔無し」）。最寄りの66kVまで約4.4km</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>・54haと広い
+・加治木(66kV)は空容量7MW・出力制御なし</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>・最寄りの送電線まで約4.4km（66kV）。220kVは約7km→自前の送電線が長く、費用が大きい
+・敷地に接する道路がない</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>見送り候補</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>1746</v>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>北茨城（KE表記：高萩）</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>山林</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>1983</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>275</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>275kVの送電線まで約13mだが、土地が0.2haしかなく特高には狭すぎる</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>・275kV送電線（2回線）まで約13m</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>・土地が1,983㎡（約0.2ha）で、275kVの受電設備を置くには狭い
+・上位の常磐(275kV)は混雑度114%、近くの66kVも空容量0
+・尾根上で道路も遠い（幅3m以上まで約1.2km）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>※送電線の位置・電圧は OpenStreetMap（OpenInfraMap）による。送電線ごとの空容量は電力会社の空容量マップで要確認。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1050,7 +1548,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1435,7 +1933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3752,7 +4250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
